--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Sviluppo economico.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Sviluppo economico.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="103">
   <si>
     <r>
       <t xml:space="preserve">
@@ -459,7 +459,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">.
-Per prenotare il tuo appuntamento, [visita questo sito](URL). 
+Per prenotare il tuo appuntamento, [visita questo sito](URL).
 Per ulteriori informazioni, [visita questo sito](URL)</t>
     </r>
   </si>
@@ -637,7 +637,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> altri documenti. 
+      <t xml:space="preserve"> altri documenti.
 Consulta il riepilogo della tua domanda, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -768,7 +768,7 @@
     <t>Aggiungi documenti</t>
   </si>
   <si>
-    <t>Vedi ricevuta</t>
+    <t>Vai alla ricevuta</t>
   </si>
   <si>
     <r>
@@ -788,7 +788,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -862,9 +862,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi dell'appuntamento tramite notifica push.</t>
   </si>
 </sst>
 </file>
@@ -1704,7 +1701,7 @@
         <v>57</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="E11" s="34" t="s">
         <v>57</v>
